--- a/Participant_Images/101/101_WTP.xlsx
+++ b/Participant_Images/101/101_WTP.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melanieruiz/Desktop/Rej_WTP_Choice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE3053B4-CBAF-8543-9519-8AE0284FF6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF8083A-5262-FB4F-B1E4-7DA4F4BEA016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="101_WTP" sheetId="1" r:id="rId1"/>
@@ -291,10 +291,6 @@
     <t>Taking a nap</t>
   </si>
   <si>
-    <t>Going shopping with
-a significant other</t>
-  </si>
-  <si>
     <t>Trying to solve a Rubik’s cube</t>
   </si>
   <si>
@@ -371,12 +367,15 @@
   </si>
   <si>
     <t>Cleaning up around the house</t>
+  </si>
+  <si>
+    <t>Going shopping with a significant other</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1213,9 +1212,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -2433,7 +2437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2441,10 +2445,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" t="s">
         <v>85</v>
-      </c>
-      <c r="D39" t="s">
-        <v>86</v>
       </c>
       <c r="E39">
         <v>0.03</v>
@@ -2473,10 +2477,10 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" t="s">
         <v>87</v>
-      </c>
-      <c r="D40" t="s">
-        <v>88</v>
       </c>
       <c r="E40">
         <v>0.04</v>
@@ -2505,10 +2509,10 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" t="s">
         <v>89</v>
-      </c>
-      <c r="D41" t="s">
-        <v>90</v>
       </c>
       <c r="E41">
         <v>0.05</v>
@@ -2537,10 +2541,10 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" t="s">
         <v>91</v>
-      </c>
-      <c r="D42" t="s">
-        <v>92</v>
       </c>
       <c r="E42">
         <v>0.01</v>
@@ -2569,10 +2573,10 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" t="s">
         <v>93</v>
-      </c>
-      <c r="D43" t="s">
-        <v>94</v>
       </c>
       <c r="E43">
         <v>0.02</v>
@@ -2601,10 +2605,10 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="E44">
         <v>0.03</v>
@@ -2633,10 +2637,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="E45">
         <v>0.04</v>
@@ -2665,10 +2669,10 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D46" t="s">
         <v>99</v>
-      </c>
-      <c r="D46" t="s">
-        <v>100</v>
       </c>
       <c r="E46">
         <v>0.05</v>
@@ -2697,10 +2701,10 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" t="s">
         <v>101</v>
-      </c>
-      <c r="D47" t="s">
-        <v>102</v>
       </c>
       <c r="E47">
         <v>0.01</v>
@@ -2729,10 +2733,10 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" t="s">
         <v>103</v>
-      </c>
-      <c r="D48" t="s">
-        <v>104</v>
       </c>
       <c r="E48">
         <v>0.02</v>
@@ -2761,10 +2765,10 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" t="s">
         <v>105</v>
-      </c>
-      <c r="D49" t="s">
-        <v>106</v>
       </c>
       <c r="E49">
         <v>0.03</v>
@@ -2793,10 +2797,10 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" t="s">
         <v>107</v>
-      </c>
-      <c r="D50" t="s">
-        <v>108</v>
       </c>
       <c r="E50">
         <v>0.04</v>
@@ -2825,10 +2829,10 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" t="s">
         <v>109</v>
-      </c>
-      <c r="D51" t="s">
-        <v>110</v>
       </c>
       <c r="E51">
         <v>0.05</v>

--- a/Participant_Images/101/101_WTP.xlsx
+++ b/Participant_Images/101/101_WTP.xlsx
@@ -8,14 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melanieruiz/Desktop/Rej_WTP_Choice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF8083A-5262-FB4F-B1E4-7DA4F4BEA016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EFB7DE4-9CC9-9649-ABB2-CF149AF6A3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{A59BDD3B-69B9-4D49-B8CD-95AA9E5B14BE}"/>
   </bookViews>
   <sheets>
-    <sheet name="101_WTP" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -67,10 +83,6 @@
     <t>Having a picnic with family</t>
   </si>
   <si>
-    <t>Painting your bedroom
-a new color</t>
-  </si>
-  <si>
     <t>Having a romantic dinner with a significant other</t>
   </si>
   <si>
@@ -86,14 +98,6 @@
     <t>Going to a friend’s birthday party</t>
   </si>
   <si>
-    <t>Listening to music
-by yourself</t>
-  </si>
-  <si>
-    <t>Giving a friend a ride
-to school</t>
-  </si>
-  <si>
     <t>Writing journal entries</t>
   </si>
   <si>
@@ -115,18 +119,6 @@
     <t>Going to the beach alone</t>
   </si>
   <si>
-    <t>Shopping for clothes
-with friends</t>
-  </si>
-  <si>
-    <t>Driving to school
-by yourself</t>
-  </si>
-  <si>
-    <t>Going to the movies
-with a significant other</t>
-  </si>
-  <si>
     <t>Doing your laundry</t>
   </si>
   <si>
@@ -136,10 +128,6 @@
     <t>Putting gas in a car</t>
   </si>
   <si>
-    <t>Going to a sporting
-event with friends</t>
-  </si>
-  <si>
     <t>Getting a haircut</t>
   </si>
   <si>
@@ -149,10 +137,6 @@
     <t>Playing a videogame at home</t>
   </si>
   <si>
-    <t>Snapchatting with
-friends</t>
-  </si>
-  <si>
     <t>Going to a farmer's market by yourself</t>
   </si>
   <si>
@@ -162,10 +146,6 @@
     <t>Running a marathon</t>
   </si>
   <si>
-    <t>Adding new friends
-on facebook</t>
-  </si>
-  <si>
     <t>Watching the news</t>
   </si>
   <si>
@@ -175,10 +155,6 @@
     <t>Going on vacation by yourself</t>
   </si>
   <si>
-    <t>Going to a work outing
-with colleagues</t>
-  </si>
-  <si>
     <t>Listening to a podcast</t>
   </si>
   <si>
@@ -194,10 +170,6 @@
     <t>Going for a bicycle ride alone</t>
   </si>
   <si>
-    <t>Going on Spring Break 
-vacation with friends</t>
-  </si>
-  <si>
     <t>Learning how to perform card tricks</t>
   </si>
   <si>
@@ -228,10 +200,6 @@
     <t>Watching Netflix at home by yourself</t>
   </si>
   <si>
-    <t>Watching television
-with family</t>
-  </si>
-  <si>
     <t>Reading news articles</t>
   </si>
   <si>
@@ -265,14 +233,6 @@
     <t>Going to the movies by yourself</t>
   </si>
   <si>
-    <t xml:space="preserve">Gaining Twitter
-followers </t>
-  </si>
-  <si>
-    <t>Taking an online
-class</t>
-  </si>
-  <si>
     <t>Spending a day at the beach with a friend</t>
   </si>
   <si>
@@ -291,6 +251,9 @@
     <t>Taking a nap</t>
   </si>
   <si>
+    <t>Going shopping with a significant other</t>
+  </si>
+  <si>
     <t>Trying to solve a Rubik’s cube</t>
   </si>
   <si>
@@ -321,18 +284,6 @@
     <t>Making breakfast for your family</t>
   </si>
   <si>
-    <t>Watching YouTube
-videos</t>
-  </si>
-  <si>
-    <t>Gaining Instagram
-followers</t>
-  </si>
-  <si>
-    <t>Getting breakfast
-by yourself</t>
-  </si>
-  <si>
     <t>Getting likes on an Instagram picture</t>
   </si>
   <si>
@@ -369,14 +320,62 @@
     <t>Cleaning up around the house</t>
   </si>
   <si>
-    <t>Going shopping with a significant other</t>
+    <t>Painting your bedroom a new color</t>
+  </si>
+  <si>
+    <t>Listening to music by yourself</t>
+  </si>
+  <si>
+    <t>Giving a friend a ride to school</t>
+  </si>
+  <si>
+    <t>Shopping for clothes with friends</t>
+  </si>
+  <si>
+    <t>Driving to school by yourself</t>
+  </si>
+  <si>
+    <t>Going to the movies with a significant other</t>
+  </si>
+  <si>
+    <t>Going to a sporting event with friends</t>
+  </si>
+  <si>
+    <t>Snapchatting with friends</t>
+  </si>
+  <si>
+    <t>Adding new friends on facebook</t>
+  </si>
+  <si>
+    <t>Going to a work outing with colleagues</t>
+  </si>
+  <si>
+    <t>Going on Spring Break vacation with friends</t>
+  </si>
+  <si>
+    <t>Watching television with family</t>
+  </si>
+  <si>
+    <t>Gaining Twitter followers</t>
+  </si>
+  <si>
+    <t>Taking an online class</t>
+  </si>
+  <si>
+    <t>Watching YouTube videos</t>
+  </si>
+  <si>
+    <t>Gaining Instagram followers</t>
+  </si>
+  <si>
+    <t>Getting breakfast by yourself</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -384,316 +383,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -701,157 +400,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -859,49 +410,8 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1212,11 +722,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40B08C40-56D8-B84A-A711-8331D3054362}">
   <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1317,7 +826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1325,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
       </c>
       <c r="E4">
         <v>0.03</v>
@@ -1357,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
       </c>
       <c r="E5">
         <v>0.04</v>
@@ -1389,10 +898,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
         <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
       </c>
       <c r="E6">
         <v>0.05</v>
@@ -1413,7 +922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1421,10 +930,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="E7">
         <v>0.01</v>
@@ -1453,10 +962,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E8">
         <v>0.02</v>
@@ -1485,10 +994,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E9">
         <v>0.03</v>
@@ -1517,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10">
         <v>0.04</v>
@@ -1541,7 +1050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1549,10 +1058,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>0.05</v>
@@ -1573,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1581,10 +1090,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="E12">
         <v>0.01</v>
@@ -1613,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E13">
         <v>0.02</v>
@@ -1637,7 +1146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1645,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>0.03</v>
@@ -1677,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <v>0.04</v>
@@ -1701,7 +1210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1709,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="E16">
         <v>0.05</v>
@@ -1741,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E17">
         <v>0.01</v>
@@ -1765,7 +1274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1773,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="E18">
         <v>0.02</v>
@@ -1805,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E19">
         <v>0.03</v>
@@ -1829,7 +1338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1837,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="E20">
         <v>0.04</v>
@@ -1869,10 +1378,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E21">
         <v>0.05</v>
@@ -1901,10 +1410,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E22">
         <v>0.01</v>
@@ -1925,7 +1434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1933,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="E23">
         <v>0.02</v>
@@ -1965,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E24">
         <v>0.03</v>
@@ -1997,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E25">
         <v>0.04</v>
@@ -2029,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E26">
         <v>0.05</v>
@@ -2061,10 +1570,10 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E27">
         <v>0.01</v>
@@ -2093,10 +1602,10 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E28">
         <v>0.02</v>
@@ -2117,7 +1626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2125,10 +1634,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E29">
         <v>0.03</v>
@@ -2157,10 +1666,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E30">
         <v>0.04</v>
@@ -2189,10 +1698,10 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E31">
         <v>0.05</v>
@@ -2221,10 +1730,10 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E32">
         <v>0.01</v>
@@ -2253,10 +1762,10 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E33">
         <v>0.02</v>
@@ -2285,10 +1794,10 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E34">
         <v>0.03</v>
@@ -2309,7 +1818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2317,10 +1826,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E35">
         <v>0.04</v>
@@ -2349,10 +1858,10 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E36">
         <v>0.05</v>
@@ -2381,10 +1890,10 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E37">
         <v>0.01</v>
@@ -2413,10 +1922,10 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E38">
         <v>0.02</v>
@@ -2445,10 +1954,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E39">
         <v>0.03</v>
@@ -2477,10 +1986,10 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E40">
         <v>0.04</v>
@@ -2509,10 +2018,10 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E41">
         <v>0.05</v>
@@ -2541,10 +2050,10 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E42">
         <v>0.01</v>
@@ -2573,10 +2082,10 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D43" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E43">
         <v>0.02</v>
@@ -2597,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2605,10 +2114,10 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E44">
         <v>0.03</v>
@@ -2629,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2637,10 +2146,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E45">
         <v>0.04</v>
@@ -2669,10 +2178,10 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="E46">
         <v>0.05</v>
@@ -2701,10 +2210,10 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="E47">
         <v>0.01</v>
@@ -2733,10 +2242,10 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D48" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E48">
         <v>0.02</v>
@@ -2765,10 +2274,10 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D49" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="E49">
         <v>0.03</v>
@@ -2797,10 +2306,10 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E50">
         <v>0.04</v>
@@ -2829,10 +2338,10 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D51" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E51">
         <v>0.05</v>
@@ -2854,6 +2363,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>